--- a/Convert_from_xlsx_to_Json/table_normalization/economy-table44.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/economy-table44.xlsx
@@ -184,7 +184,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -314,11 +314,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="168" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
     </xf>
@@ -326,6 +326,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
@@ -335,7 +336,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -612,31 +612,34 @@
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="35.36328125" style="1" customWidth="1"/>
-    <col min="2" max="4" width="8.6328125" style="1"/>
+    <col min="2" max="2" width="8.6328125" style="1"/>
+    <col min="3" max="3" width="11.54296875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.6328125" style="1"/>
     <col min="5" max="5" width="33.54296875" style="1" customWidth="1"/>
-    <col min="6" max="7" width="8.6328125" style="1"/>
+    <col min="6" max="6" width="8.6328125" style="1"/>
+    <col min="7" max="7" width="11.81640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="11.7265625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="11.08984375" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13" style="1" customWidth="1"/>
     <col min="10" max="10" width="8.6328125" style="1"/>
     <col min="11" max="11" width="12.26953125" style="1" customWidth="1"/>
     <col min="12" max="16384" width="8.6328125" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="14"/>
-      <c r="E1" s="12" t="s">
+      <c r="B1" s="14"/>
+      <c r="C1" s="15"/>
+      <c r="E1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="13"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="15" t="s">
+      <c r="F1" s="14"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="12" t="s">
         <v>3</v>
       </c>
       <c r="K1" s="9" t="s">
